--- a/students.xlsx
+++ b/students.xlsx
@@ -1,70 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f25aa4a93b616c7/Documents/git_assignment/excel_automation/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2B59059F12C24C4B9BEA4033451510344D07F328" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Students" sheetId="1" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Marks</t>
-  </si>
-  <si>
-    <t>AGE</t>
-  </si>
-  <si>
-    <t>Nikhitha</t>
-  </si>
-  <si>
-    <t>Rahul</t>
-  </si>
-  <si>
-    <t>Priya</t>
-  </si>
-  <si>
-    <t>Kiran</t>
-  </si>
-  <si>
-    <t>Anu</t>
-  </si>
-  <si>
-    <t>Ravi</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -83,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -385,96 +407,159 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Marks</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Nikhitha</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>90</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rahul</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>85</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>95</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>78</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Anu</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>88</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>91</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>91</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sita</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>76</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Meena</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>93</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/students.xlsx
+++ b/students.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -439,7 +439,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
         <v>22</v>
@@ -559,6 +559,58 @@
         <v>93</v>
       </c>
       <c r="C11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>91</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sita</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>87</v>
+      </c>
+      <c r="C13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>76</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Meena</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>93</v>
+      </c>
+      <c r="C15" t="n">
         <v>20</v>
       </c>
     </row>

--- a/students.xlsx
+++ b/students.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4800" yWindow="510" windowWidth="14400" windowHeight="10770" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -431,6 +431,11 @@
           <t>AGE</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -444,6 +449,11 @@
       <c r="C2" t="n">
         <v>22</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,6 +467,11 @@
       <c r="C3" t="n">
         <v>24</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,6 +485,11 @@
       <c r="C4" t="n">
         <v>27</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,6 +503,11 @@
       <c r="C5" t="n">
         <v>21</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,6 +521,11 @@
       <c r="C6" t="n">
         <v>19</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,6 +539,11 @@
       <c r="C7" t="n">
         <v>23</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,6 +557,11 @@
       <c r="C8" t="n">
         <v>23</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,6 +575,11 @@
       <c r="C9" t="n">
         <v>21</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,6 +593,11 @@
       <c r="C10" t="n">
         <v>22</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,6 +611,11 @@
       <c r="C11" t="n">
         <v>20</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,6 +629,11 @@
       <c r="C12" t="n">
         <v>23</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,6 +647,11 @@
       <c r="C13" t="n">
         <v>21</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,6 +665,11 @@
       <c r="C14" t="n">
         <v>22</v>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -612,6 +682,11 @@
       </c>
       <c r="C15" t="n">
         <v>20</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/students.xlsx
+++ b/students.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -692,4 +693,25 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Student Summary</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/students.xlsx
+++ b/students.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,28 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +54,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -413,278 +441,299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>AGE</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Nikhitha</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Rahul</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Kiran</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Anu</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Sita</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Arjun</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Meena</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Sita</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Arjun</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Meena</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -701,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +760,46 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Students</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Average Marks</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>87.57142857142857</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Highest Marks</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lowest Marks</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/students.xlsx
+++ b/students.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -64,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -76,6 +81,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -457,17 +468,18 @@
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>AGE</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -480,51 +492,40 @@
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Rahul</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Rahul</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n">
-        <v>95</v>
-      </c>
+      <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="E4" t="inlineStr">
+        <v>85</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -533,17 +534,18 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n">
-        <v>78</v>
-      </c>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E5" t="inlineStr">
+        <v>95</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -552,17 +554,18 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Anu</t>
+          <t>Kiran</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n">
-        <v>88</v>
-      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="E6" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -571,17 +574,18 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Anu</t>
         </is>
       </c>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n">
-        <v>91</v>
-      </c>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="E7" t="inlineStr">
+        <v>88</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -594,13 +598,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -609,17 +614,18 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Sita</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n">
-        <v>87</v>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>91</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -628,17 +634,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Sita</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n">
-        <v>76</v>
-      </c>
+      <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E10" t="inlineStr">
+        <v>87</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -647,17 +654,18 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Meena</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n">
-        <v>93</v>
-      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" t="inlineStr">
+        <v>76</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -666,17 +674,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Ravi</t>
+          <t>Meena</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n">
-        <v>91</v>
-      </c>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="E12" t="inlineStr">
+        <v>93</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -685,17 +694,18 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Sita</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n">
-        <v>87</v>
-      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E13" t="inlineStr">
+        <v>91</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -704,17 +714,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Sita</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n">
-        <v>76</v>
-      </c>
+      <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E14" t="inlineStr">
+        <v>87</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -723,17 +734,38 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Meena</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -752,51 +784,56 @@
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Student Summary</t>
         </is>
       </c>
+      <c r="B1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Total Students</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Average Marks</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="8" t="n">
         <v>87.57142857142857</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Highest Marks</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>95</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Lowest Marks</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>76</v>
       </c>
     </row>

--- a/students.xlsx
+++ b/students.xlsx
@@ -3,21 +3,23 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4800" yWindow="510" windowWidth="14400" windowHeight="10770" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$F$16</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,7 +28,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,8 +53,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +66,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -60,18 +84,69 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -87,6 +162,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,326 +546,298 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>AGE</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Result</t>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Statistics</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Nikhitha</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Total Marks</t>
+        </is>
+      </c>
+      <c r="I2" s="9">
+        <f>SUM(D2:D16)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Average Marks</t>
+        </is>
+      </c>
+      <c r="I3" s="13">
+        <f>AVERAGE(D2:D16)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Rahul</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Highest Marks</t>
+        </is>
+      </c>
+      <c r="I4" s="9">
+        <f>MAX(D2:D16)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>Lowest Marks</t>
+        </is>
+      </c>
+      <c r="I5" s="9">
+        <f>MIN(D2:D16)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Kiran</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Anu</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="9" t="n">
         <v>88</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n">
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Sita</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n">
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Arjun</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n">
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="9" t="n">
         <v>76</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Meena</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n">
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="9" t="n">
         <v>93</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Ravi</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n">
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Sita</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n">
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Arjun</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n">
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="9" t="n">
         <v>76</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Meena</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n">
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="9" t="n">
         <v>93</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -783,61 +849,64 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Student Summary</t>
         </is>
       </c>
-      <c r="B1" s="6" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="B1" s="11" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Total Students</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="9" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Average Marks</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="13" t="n">
         <v>87.57142857142857</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Highest Marks</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="9" t="n">
         <v>95</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Lowest Marks</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="9" t="n">
         <v>76</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>